--- a/vending_machine_refactor/data/vending_machine_gui_demo.xlsx
+++ b/vending_machine_refactor/data/vending_machine_gui_demo.xlsx
@@ -1,35 +1,49 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="3" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="products" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="cash_inventory" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="machine_config" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="session_state" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="sales_log" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="cash_log" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="stock_log" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="audit_log" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="products" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="cash_inventory" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="machine_config" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="session_state" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="sales_log" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="cash_log" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="stock_log" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="audit_log" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="4">
     <font>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
+      <sz val="8"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -37,12 +51,17 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F4E78"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -62,14 +81,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -433,9 +455,9 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:H7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="1" max="6"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
@@ -446,42 +468,42 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>product_id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>stock</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>max_stock</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>image_path</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" s="2" t="inlineStr">
         <is>
           <t>slot_no</t>
         </is>
@@ -499,7 +521,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2200</v>
+        <v>480</v>
       </c>
       <c r="D2" t="n">
         <v>10</v>
@@ -533,7 +555,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="D3" t="n">
         <v>10</v>
@@ -567,7 +589,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1800</v>
+        <v>550</v>
       </c>
       <c r="D4" t="n">
         <v>10</v>
@@ -601,7 +623,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1200</v>
+        <v>700</v>
       </c>
       <c r="D5" t="n">
         <v>10</v>
@@ -635,7 +657,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1300</v>
+        <v>750</v>
       </c>
       <c r="D6" t="n">
         <v>10</v>
@@ -669,10 +691,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2500</v>
+        <v>800</v>
       </c>
       <c r="D7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E7" t="n">
         <v>10</v>
@@ -703,37 +725,37 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="2" max="3"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>denomination</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>min_keep</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>max_capacity</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>kind</t>
         </is>
@@ -744,7 +766,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C2" t="n">
         <v>15</v>
@@ -763,7 +785,7 @@
         <v>50</v>
       </c>
       <c r="B3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C3" t="n">
         <v>10</v>
@@ -801,7 +823,7 @@
         <v>500</v>
       </c>
       <c r="B5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C5" t="n">
         <v>8</v>
@@ -820,7 +842,7 @@
         <v>1000</v>
       </c>
       <c r="B6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C6" t="n">
         <v>5</v>
@@ -846,19 +868,19 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:B7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>key</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>value</t>
         </is>
@@ -948,19 +970,19 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:B7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>key</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>value</t>
         </is>
@@ -973,7 +995,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>18500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -1013,7 +1035,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -1023,7 +1045,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1037,14 +1059,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I215"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:I216"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
     <col width="21" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="5" max="6"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="15" customWidth="1" min="8" max="8"/>
@@ -1052,47 +1074,47 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>sale_id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>sold_at</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>product_id</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>product_name</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>unit_price</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>qty</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>paid_amount</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" s="2" t="inlineStr">
         <is>
           <t>change_amount</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" s="2" t="inlineStr">
         <is>
           <t>result</t>
         </is>
@@ -9439,6 +9461,45 @@
         <v>1420</v>
       </c>
       <c r="I215" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>SALE-20260325231634240711</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>2026-03-25 23:16:34</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>P006</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>특화음료</t>
+        </is>
+      </c>
+      <c r="E216" t="n">
+        <v>800</v>
+      </c>
+      <c r="F216" t="n">
+        <v>1</v>
+      </c>
+      <c r="G216" t="n">
+        <v>800</v>
+      </c>
+      <c r="H216" t="n">
+        <v>0</v>
+      </c>
+      <c r="I216" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
@@ -9455,50 +9516,50 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G319"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:G346"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
     <col width="21" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="5" max="6"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="24" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>cash_event_id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>event_at</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>event_type</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>denomination</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>qty</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>amount</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -19357,6 +19418,843 @@
         <v>1000</v>
       </c>
       <c r="G319" t="inlineStr">
+        <is>
+          <t>user_insert</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>CASH-20260325230155120349</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>2026-03-25 23:01:55</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>INSERT</t>
+        </is>
+      </c>
+      <c r="D320" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E320" t="n">
+        <v>1</v>
+      </c>
+      <c r="F320" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G320" t="inlineStr">
+        <is>
+          <t>user_insert</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>CASH-20260325230854550032</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>2026-03-25 23:08:54</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>INSERT</t>
+        </is>
+      </c>
+      <c r="D321" t="n">
+        <v>10</v>
+      </c>
+      <c r="E321" t="n">
+        <v>1</v>
+      </c>
+      <c r="F321" t="n">
+        <v>10</v>
+      </c>
+      <c r="G321" t="inlineStr">
+        <is>
+          <t>user_insert</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>CASH-20260325230913475645</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>2026-03-25 23:09:13</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>COLLECT</t>
+        </is>
+      </c>
+      <c r="D322" t="n">
+        <v>10</v>
+      </c>
+      <c r="E322" t="n">
+        <v>1</v>
+      </c>
+      <c r="F322" t="n">
+        <v>10</v>
+      </c>
+      <c r="G322" t="inlineStr">
+        <is>
+          <t>admin_collect_keep_min</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>CASH-20260325230913475667</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>2026-03-25 23:09:13</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>COLLECT</t>
+        </is>
+      </c>
+      <c r="D323" t="n">
+        <v>500</v>
+      </c>
+      <c r="E323" t="n">
+        <v>1</v>
+      </c>
+      <c r="F323" t="n">
+        <v>500</v>
+      </c>
+      <c r="G323" t="inlineStr">
+        <is>
+          <t>admin_collect_keep_min</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>CASH-20260325230913475677</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>2026-03-25 23:09:13</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>COLLECT</t>
+        </is>
+      </c>
+      <c r="D324" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E324" t="n">
+        <v>3</v>
+      </c>
+      <c r="F324" t="n">
+        <v>3000</v>
+      </c>
+      <c r="G324" t="inlineStr">
+        <is>
+          <t>admin_collect_keep_min</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>CASH-20260325230927376574</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>2026-03-25 23:09:27</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>INSERT</t>
+        </is>
+      </c>
+      <c r="D325" t="n">
+        <v>10</v>
+      </c>
+      <c r="E325" t="n">
+        <v>1</v>
+      </c>
+      <c r="F325" t="n">
+        <v>10</v>
+      </c>
+      <c r="G325" t="inlineStr">
+        <is>
+          <t>user_insert</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>CASH-20260325230928278701</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>2026-03-25 23:09:28</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>INSERT</t>
+        </is>
+      </c>
+      <c r="D326" t="n">
+        <v>50</v>
+      </c>
+      <c r="E326" t="n">
+        <v>1</v>
+      </c>
+      <c r="F326" t="n">
+        <v>50</v>
+      </c>
+      <c r="G326" t="inlineStr">
+        <is>
+          <t>user_insert</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>CASH-20260325231608702088</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>2026-03-25 23:16:08</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>INSERT</t>
+        </is>
+      </c>
+      <c r="D327" t="n">
+        <v>10</v>
+      </c>
+      <c r="E327" t="n">
+        <v>1</v>
+      </c>
+      <c r="F327" t="n">
+        <v>10</v>
+      </c>
+      <c r="G327" t="inlineStr">
+        <is>
+          <t>user_insert</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>CASH-20260325231611983984</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>2026-03-25 23:16:11</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>INSERT</t>
+        </is>
+      </c>
+      <c r="D328" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E328" t="n">
+        <v>1</v>
+      </c>
+      <c r="F328" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G328" t="inlineStr">
+        <is>
+          <t>user_insert</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>CASH-20260325231612985829</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>2026-03-25 23:16:12</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>INSERT</t>
+        </is>
+      </c>
+      <c r="D329" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E329" t="n">
+        <v>1</v>
+      </c>
+      <c r="F329" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G329" t="inlineStr">
+        <is>
+          <t>user_insert</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>CASH-20260325231613991287</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>2026-03-25 23:16:13</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>INSERT</t>
+        </is>
+      </c>
+      <c r="D330" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E330" t="n">
+        <v>1</v>
+      </c>
+      <c r="F330" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G330" t="inlineStr">
+        <is>
+          <t>user_insert</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>CASH-20260325231615180728</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>2026-03-25 23:16:15</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>INSERT</t>
+        </is>
+      </c>
+      <c r="D331" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E331" t="n">
+        <v>1</v>
+      </c>
+      <c r="F331" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G331" t="inlineStr">
+        <is>
+          <t>user_insert</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>CASH-20260325231616215458</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>2026-03-25 23:16:16</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>INSERT</t>
+        </is>
+      </c>
+      <c r="D332" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E332" t="n">
+        <v>1</v>
+      </c>
+      <c r="F332" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G332" t="inlineStr">
+        <is>
+          <t>user_insert</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>CASH-20260325231617376037</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>2026-03-25 23:16:17</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>INSERT</t>
+        </is>
+      </c>
+      <c r="D333" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E333" t="n">
+        <v>1</v>
+      </c>
+      <c r="F333" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G333" t="inlineStr">
+        <is>
+          <t>user_insert</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>CASH-20260325231618164906</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>2026-03-25 23:16:18</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>INSERT</t>
+        </is>
+      </c>
+      <c r="D334" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E334" t="n">
+        <v>1</v>
+      </c>
+      <c r="F334" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G334" t="inlineStr">
+        <is>
+          <t>user_insert</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>CASH-20260325231619301505</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>2026-03-25 23:16:19</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>INSERT</t>
+        </is>
+      </c>
+      <c r="D335" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E335" t="n">
+        <v>1</v>
+      </c>
+      <c r="F335" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G335" t="inlineStr">
+        <is>
+          <t>user_insert</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>CASH-20260325231620688336</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>2026-03-25 23:16:20</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>INSERT</t>
+        </is>
+      </c>
+      <c r="D336" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E336" t="n">
+        <v>1</v>
+      </c>
+      <c r="F336" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G336" t="inlineStr">
+        <is>
+          <t>user_insert</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>CASH-20260325231622014564</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>2026-03-25 23:16:22</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>INSERT</t>
+        </is>
+      </c>
+      <c r="D337" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E337" t="n">
+        <v>1</v>
+      </c>
+      <c r="F337" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G337" t="inlineStr">
+        <is>
+          <t>user_insert</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>CASH-20260325231622946961</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>2026-03-25 23:16:22</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>INSERT</t>
+        </is>
+      </c>
+      <c r="D338" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E338" t="n">
+        <v>1</v>
+      </c>
+      <c r="F338" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G338" t="inlineStr">
+        <is>
+          <t>user_insert</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>CASH-20260325231623797241</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>2026-03-25 23:16:23</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>INSERT</t>
+        </is>
+      </c>
+      <c r="D339" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E339" t="n">
+        <v>1</v>
+      </c>
+      <c r="F339" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G339" t="inlineStr">
+        <is>
+          <t>user_insert</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>CASH-20260325231624720856</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>2026-03-25 23:16:24</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>INSERT</t>
+        </is>
+      </c>
+      <c r="D340" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E340" t="n">
+        <v>1</v>
+      </c>
+      <c r="F340" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G340" t="inlineStr">
+        <is>
+          <t>user_insert</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>CASH-20260325231625569056</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>2026-03-25 23:16:25</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>INSERT</t>
+        </is>
+      </c>
+      <c r="D341" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E341" t="n">
+        <v>1</v>
+      </c>
+      <c r="F341" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G341" t="inlineStr">
+        <is>
+          <t>user_insert</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>CASH-20260325231626390317</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>2026-03-25 23:16:26</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>INSERT</t>
+        </is>
+      </c>
+      <c r="D342" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E342" t="n">
+        <v>1</v>
+      </c>
+      <c r="F342" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G342" t="inlineStr">
+        <is>
+          <t>user_insert</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>CASH-20260325231627141304</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>2026-03-25 23:16:27</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>INSERT</t>
+        </is>
+      </c>
+      <c r="D343" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E343" t="n">
+        <v>1</v>
+      </c>
+      <c r="F343" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G343" t="inlineStr">
+        <is>
+          <t>user_insert</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>CASH-20260325231628113419</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>2026-03-25 23:16:28</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>REFUND</t>
+        </is>
+      </c>
+      <c r="D344" t="n">
+        <v>10</v>
+      </c>
+      <c r="E344" t="n">
+        <v>1</v>
+      </c>
+      <c r="F344" t="n">
+        <v>10</v>
+      </c>
+      <c r="G344" t="inlineStr">
+        <is>
+          <t>user_refund</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>CASH-20260325231628113436</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>2026-03-25 23:16:28</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>REFUND</t>
+        </is>
+      </c>
+      <c r="D345" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E345" t="n">
+        <v>16</v>
+      </c>
+      <c r="F345" t="n">
+        <v>16000</v>
+      </c>
+      <c r="G345" t="inlineStr">
+        <is>
+          <t>user_refund</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>CASH-20260325231631282812</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>2026-03-25 23:16:31</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>INSERT</t>
+        </is>
+      </c>
+      <c r="D346" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E346" t="n">
+        <v>1</v>
+      </c>
+      <c r="F346" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G346" t="inlineStr">
         <is>
           <t>user_insert</t>
         </is>
@@ -19373,8 +20271,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:I10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
     <col width="21" customWidth="1" min="2" max="2"/>
@@ -19388,47 +20286,47 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>stock_event_id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>event_at</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>product_id</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>product_name</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>event_type</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>before_stock</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>change_qty</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" s="2" t="inlineStr">
         <is>
           <t>after_stock</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" s="2" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -19759,6 +20657,47 @@
       <c r="I9" t="inlineStr">
         <is>
           <t>admin_refill_to_max</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>STOCK-20260325231634240735</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-03-25 23:16:34</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>P006</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>특화음료</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>SALE</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>10</v>
+      </c>
+      <c r="G10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H10" t="n">
+        <v>9</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>purchase</t>
         </is>
       </c>
     </row>
@@ -19773,8 +20712,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:F13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
     <col width="21" customWidth="1" min="2" max="2"/>
@@ -19785,32 +20724,32 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>audit_id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>event_at</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>actor</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>action</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>target</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>detail</t>
         </is>
@@ -20165,6 +21104,38 @@
       <c r="F12" t="inlineStr">
         <is>
           <t>keep_minimum=True, total_amount=16000</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>AUDIT-20260325230913475689</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-03-25 23:09:13</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>CASH_COLLECT</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>cash_inventory</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>keep_minimum=True, total_amount=3510</t>
         </is>
       </c>
     </row>
